--- a/CATI/saved_states/NABIL_backtest_results.xlsx
+++ b/CATI/saved_states/NABIL_backtest_results.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Backtest_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metrics" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Confusion_Matrix" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Feature_Importance" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Backtest_Metrics" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Backtest" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Confusion" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Feature_Importance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Metrics" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -449,7 +448,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Ensemble_Pred</t>
+          <t>Prediction</t>
         </is>
       </c>
     </row>
@@ -460,8 +459,10 @@
       <c r="B2" t="n">
         <v>517</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -471,8 +472,10 @@
       <c r="B3" t="n">
         <v>511.9</v>
       </c>
-      <c r="C3" t="n">
-        <v>1</v>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -482,8 +485,10 @@
       <c r="B4" t="n">
         <v>508.9</v>
       </c>
-      <c r="C4" t="n">
-        <v>1</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -493,8 +498,10 @@
       <c r="B5" t="n">
         <v>506</v>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -504,8 +511,10 @@
       <c r="B6" t="n">
         <v>502</v>
       </c>
-      <c r="C6" t="n">
-        <v>1</v>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -515,8 +524,10 @@
       <c r="B7" t="n">
         <v>502.1</v>
       </c>
-      <c r="C7" t="n">
-        <v>1</v>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -526,8 +537,10 @@
       <c r="B8" t="n">
         <v>505</v>
       </c>
-      <c r="C8" t="n">
-        <v>1</v>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -537,8 +550,10 @@
       <c r="B9" t="n">
         <v>507.6</v>
       </c>
-      <c r="C9" t="n">
-        <v>1</v>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -548,8 +563,10 @@
       <c r="B10" t="n">
         <v>528.5</v>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -559,8 +576,10 @@
       <c r="B11" t="n">
         <v>522</v>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -570,8 +589,10 @@
       <c r="B12" t="n">
         <v>521.2</v>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -581,8 +602,10 @@
       <c r="B13" t="n">
         <v>521</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -592,8 +615,10 @@
       <c r="B14" t="n">
         <v>522.8</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -603,8 +628,10 @@
       <c r="B15" t="n">
         <v>513</v>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -614,8 +641,10 @@
       <c r="B16" t="n">
         <v>513</v>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -625,8 +654,10 @@
       <c r="B17" t="n">
         <v>518</v>
       </c>
-      <c r="C17" t="n">
-        <v>1</v>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -636,8 +667,10 @@
       <c r="B18" t="n">
         <v>520</v>
       </c>
-      <c r="C18" t="n">
-        <v>1</v>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -647,8 +680,10 @@
       <c r="B19" t="n">
         <v>523</v>
       </c>
-      <c r="C19" t="n">
-        <v>1</v>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -658,8 +693,10 @@
       <c r="B20" t="n">
         <v>515</v>
       </c>
-      <c r="C20" t="n">
-        <v>1</v>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -669,8 +706,10 @@
       <c r="B21" t="n">
         <v>508</v>
       </c>
-      <c r="C21" t="n">
-        <v>1</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -680,8 +719,10 @@
       <c r="B22" t="n">
         <v>506</v>
       </c>
-      <c r="C22" t="n">
-        <v>1</v>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -691,8 +732,10 @@
       <c r="B23" t="n">
         <v>505.9</v>
       </c>
-      <c r="C23" t="n">
-        <v>1</v>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -702,8 +745,10 @@
       <c r="B24" t="n">
         <v>499.9</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -713,8 +758,10 @@
       <c r="B25" t="n">
         <v>496</v>
       </c>
-      <c r="C25" t="n">
-        <v>1</v>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -724,8 +771,10 @@
       <c r="B26" t="n">
         <v>495.5</v>
       </c>
-      <c r="C26" t="n">
-        <v>1</v>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -735,8 +784,10 @@
       <c r="B27" t="n">
         <v>490</v>
       </c>
-      <c r="C27" t="n">
-        <v>1</v>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -746,8 +797,10 @@
       <c r="B28" t="n">
         <v>488.1</v>
       </c>
-      <c r="C28" t="n">
-        <v>1</v>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -757,8 +810,10 @@
       <c r="B29" t="n">
         <v>490</v>
       </c>
-      <c r="C29" t="n">
-        <v>1</v>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -768,8 +823,10 @@
       <c r="B30" t="n">
         <v>492</v>
       </c>
-      <c r="C30" t="n">
-        <v>1</v>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -779,8 +836,10 @@
       <c r="B31" t="n">
         <v>493</v>
       </c>
-      <c r="C31" t="n">
-        <v>1</v>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -790,8 +849,10 @@
       <c r="B32" t="n">
         <v>494.5</v>
       </c>
-      <c r="C32" t="n">
-        <v>1</v>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -801,8 +862,10 @@
       <c r="B33" t="n">
         <v>501</v>
       </c>
-      <c r="C33" t="n">
-        <v>1</v>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -812,8 +875,10 @@
       <c r="B34" t="n">
         <v>504</v>
       </c>
-      <c r="C34" t="n">
-        <v>1</v>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -823,8 +888,10 @@
       <c r="B35" t="n">
         <v>498</v>
       </c>
-      <c r="C35" t="n">
-        <v>1</v>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -834,8 +901,10 @@
       <c r="B36" t="n">
         <v>493</v>
       </c>
-      <c r="C36" t="n">
-        <v>1</v>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -845,8 +914,10 @@
       <c r="B37" t="n">
         <v>489</v>
       </c>
-      <c r="C37" t="n">
-        <v>1</v>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -856,8 +927,10 @@
       <c r="B38" t="n">
         <v>484.5</v>
       </c>
-      <c r="C38" t="n">
-        <v>1</v>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -867,8 +940,10 @@
       <c r="B39" t="n">
         <v>484.9</v>
       </c>
-      <c r="C39" t="n">
-        <v>1</v>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -878,8 +953,10 @@
       <c r="B40" t="n">
         <v>488</v>
       </c>
-      <c r="C40" t="n">
-        <v>0</v>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -889,8 +966,10 @@
       <c r="B41" t="n">
         <v>491</v>
       </c>
-      <c r="C41" t="n">
-        <v>0</v>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -900,8 +979,10 @@
       <c r="B42" t="n">
         <v>488</v>
       </c>
-      <c r="C42" t="n">
-        <v>0</v>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -911,8 +992,10 @@
       <c r="B43" t="n">
         <v>487</v>
       </c>
-      <c r="C43" t="n">
-        <v>0</v>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -922,8 +1005,10 @@
       <c r="B44" t="n">
         <v>484.6</v>
       </c>
-      <c r="C44" t="n">
-        <v>0</v>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -933,8 +1018,10 @@
       <c r="B45" t="n">
         <v>480.6</v>
       </c>
-      <c r="C45" t="n">
-        <v>0</v>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -944,8 +1031,10 @@
       <c r="B46" t="n">
         <v>477</v>
       </c>
-      <c r="C46" t="n">
-        <v>0</v>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -955,8 +1044,10 @@
       <c r="B47" t="n">
         <v>475</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -966,8 +1057,10 @@
       <c r="B48" t="n">
         <v>475</v>
       </c>
-      <c r="C48" t="n">
-        <v>0</v>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -977,8 +1070,10 @@
       <c r="B49" t="n">
         <v>475.1</v>
       </c>
-      <c r="C49" t="n">
-        <v>0</v>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -988,8 +1083,10 @@
       <c r="B50" t="n">
         <v>475</v>
       </c>
-      <c r="C50" t="n">
-        <v>0</v>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -999,8 +1096,10 @@
       <c r="B51" t="n">
         <v>477</v>
       </c>
-      <c r="C51" t="n">
-        <v>0</v>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -1010,8 +1109,10 @@
       <c r="B52" t="n">
         <v>471.5</v>
       </c>
-      <c r="C52" t="n">
-        <v>0</v>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -1021,8 +1122,10 @@
       <c r="B53" t="n">
         <v>462.5</v>
       </c>
-      <c r="C53" t="n">
-        <v>0</v>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -1032,8 +1135,10 @@
       <c r="B54" t="n">
         <v>457.7</v>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -1043,8 +1148,10 @@
       <c r="B55" t="n">
         <v>449</v>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1054,8 +1161,10 @@
       <c r="B56" t="n">
         <v>449</v>
       </c>
-      <c r="C56" t="n">
-        <v>1</v>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -1065,8 +1174,10 @@
       <c r="B57" t="n">
         <v>445</v>
       </c>
-      <c r="C57" t="n">
-        <v>1</v>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -1076,8 +1187,10 @@
       <c r="B58" t="n">
         <v>436.5</v>
       </c>
-      <c r="C58" t="n">
-        <v>1</v>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -1087,8 +1200,10 @@
       <c r="B59" t="n">
         <v>434</v>
       </c>
-      <c r="C59" t="n">
-        <v>1</v>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -1098,8 +1213,10 @@
       <c r="B60" t="n">
         <v>437.8</v>
       </c>
-      <c r="C60" t="n">
-        <v>1</v>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -1109,8 +1226,10 @@
       <c r="B61" t="n">
         <v>435</v>
       </c>
-      <c r="C61" t="n">
-        <v>1</v>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -1120,8 +1239,10 @@
       <c r="B62" t="n">
         <v>429.5</v>
       </c>
-      <c r="C62" t="n">
-        <v>1</v>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -1131,8 +1252,10 @@
       <c r="B63" t="n">
         <v>424</v>
       </c>
-      <c r="C63" t="n">
-        <v>1</v>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -1142,8 +1265,10 @@
       <c r="B64" t="n">
         <v>458.3</v>
       </c>
-      <c r="C64" t="n">
-        <v>1</v>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -1153,8 +1278,10 @@
       <c r="B65" t="n">
         <v>446</v>
       </c>
-      <c r="C65" t="n">
-        <v>1</v>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -1164,8 +1291,10 @@
       <c r="B66" t="n">
         <v>442</v>
       </c>
-      <c r="C66" t="n">
-        <v>1</v>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1175,8 +1304,10 @@
       <c r="B67" t="n">
         <v>445.5</v>
       </c>
-      <c r="C67" t="n">
-        <v>1</v>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -1186,8 +1317,10 @@
       <c r="B68" t="n">
         <v>449.8</v>
       </c>
-      <c r="C68" t="n">
-        <v>1</v>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1197,8 +1330,10 @@
       <c r="B69" t="n">
         <v>469</v>
       </c>
-      <c r="C69" t="n">
-        <v>1</v>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -1208,8 +1343,10 @@
       <c r="B70" t="n">
         <v>473</v>
       </c>
-      <c r="C70" t="n">
-        <v>1</v>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -1219,8 +1356,10 @@
       <c r="B71" t="n">
         <v>471.9</v>
       </c>
-      <c r="C71" t="n">
-        <v>1</v>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -1230,8 +1369,10 @@
       <c r="B72" t="n">
         <v>464</v>
       </c>
-      <c r="C72" t="n">
-        <v>1</v>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -1241,8 +1382,10 @@
       <c r="B73" t="n">
         <v>461</v>
       </c>
-      <c r="C73" t="n">
-        <v>1</v>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -1252,8 +1395,10 @@
       <c r="B74" t="n">
         <v>460</v>
       </c>
-      <c r="C74" t="n">
-        <v>1</v>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -1263,8 +1408,10 @@
       <c r="B75" t="n">
         <v>457</v>
       </c>
-      <c r="C75" t="n">
-        <v>1</v>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -1274,8 +1421,10 @@
       <c r="B76" t="n">
         <v>451</v>
       </c>
-      <c r="C76" t="n">
-        <v>1</v>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -1285,8 +1434,10 @@
       <c r="B77" t="n">
         <v>445</v>
       </c>
-      <c r="C77" t="n">
-        <v>1</v>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1296,8 +1447,10 @@
       <c r="B78" t="n">
         <v>441.8</v>
       </c>
-      <c r="C78" t="n">
-        <v>1</v>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -1307,8 +1460,10 @@
       <c r="B79" t="n">
         <v>440.5</v>
       </c>
-      <c r="C79" t="n">
-        <v>1</v>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -1318,8 +1473,10 @@
       <c r="B80" t="n">
         <v>442.5</v>
       </c>
-      <c r="C80" t="n">
-        <v>1</v>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -1329,8 +1486,10 @@
       <c r="B81" t="n">
         <v>440</v>
       </c>
-      <c r="C81" t="n">
-        <v>1</v>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -1340,8 +1499,10 @@
       <c r="B82" t="n">
         <v>439</v>
       </c>
-      <c r="C82" t="n">
-        <v>1</v>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -1351,8 +1512,10 @@
       <c r="B83" t="n">
         <v>436</v>
       </c>
-      <c r="C83" t="n">
-        <v>1</v>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -1362,8 +1525,10 @@
       <c r="B84" t="n">
         <v>434</v>
       </c>
-      <c r="C84" t="n">
-        <v>1</v>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -1373,8 +1538,10 @@
       <c r="B85" t="n">
         <v>434</v>
       </c>
-      <c r="C85" t="n">
-        <v>1</v>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -1384,8 +1551,10 @@
       <c r="B86" t="n">
         <v>438</v>
       </c>
-      <c r="C86" t="n">
-        <v>1</v>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -1395,8 +1564,10 @@
       <c r="B87" t="n">
         <v>439</v>
       </c>
-      <c r="C87" t="n">
-        <v>1</v>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -1406,8 +1577,10 @@
       <c r="B88" t="n">
         <v>438</v>
       </c>
-      <c r="C88" t="n">
-        <v>1</v>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -1417,8 +1590,10 @@
       <c r="B89" t="n">
         <v>438</v>
       </c>
-      <c r="C89" t="n">
-        <v>1</v>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -1428,8 +1603,10 @@
       <c r="B90" t="n">
         <v>435</v>
       </c>
-      <c r="C90" t="n">
-        <v>1</v>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -1439,8 +1616,10 @@
       <c r="B91" t="n">
         <v>433</v>
       </c>
-      <c r="C91" t="n">
-        <v>1</v>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -1450,8 +1629,10 @@
       <c r="B92" t="n">
         <v>429.9</v>
       </c>
-      <c r="C92" t="n">
-        <v>1</v>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -1461,8 +1642,10 @@
       <c r="B93" t="n">
         <v>428</v>
       </c>
-      <c r="C93" t="n">
-        <v>1</v>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -1472,8 +1655,10 @@
       <c r="B94" t="n">
         <v>429</v>
       </c>
-      <c r="C94" t="n">
-        <v>1</v>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -1483,8 +1668,10 @@
       <c r="B95" t="n">
         <v>429</v>
       </c>
-      <c r="C95" t="n">
-        <v>1</v>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -1494,8 +1681,10 @@
       <c r="B96" t="n">
         <v>427.3</v>
       </c>
-      <c r="C96" t="n">
-        <v>1</v>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -1505,8 +1694,10 @@
       <c r="B97" t="n">
         <v>427</v>
       </c>
-      <c r="C97" t="n">
-        <v>0</v>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -1516,8 +1707,10 @@
       <c r="B98" t="n">
         <v>429</v>
       </c>
-      <c r="C98" t="n">
-        <v>0</v>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -1527,8 +1720,10 @@
       <c r="B99" t="n">
         <v>431.5</v>
       </c>
-      <c r="C99" t="n">
-        <v>0</v>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -1538,8 +1733,10 @@
       <c r="B100" t="n">
         <v>429.5</v>
       </c>
-      <c r="C100" t="n">
-        <v>0</v>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -1549,8 +1746,10 @@
       <c r="B101" t="n">
         <v>426</v>
       </c>
-      <c r="C101" t="n">
-        <v>1</v>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -1560,8 +1759,10 @@
       <c r="B102" t="n">
         <v>424</v>
       </c>
-      <c r="C102" t="n">
-        <v>1</v>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -1571,8 +1772,10 @@
       <c r="B103" t="n">
         <v>422</v>
       </c>
-      <c r="C103" t="n">
-        <v>1</v>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -1582,8 +1785,10 @@
       <c r="B104" t="n">
         <v>424.5</v>
       </c>
-      <c r="C104" t="n">
-        <v>0</v>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -1593,8 +1798,10 @@
       <c r="B105" t="n">
         <v>422.7</v>
       </c>
-      <c r="C105" t="n">
-        <v>0</v>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -1604,8 +1811,10 @@
       <c r="B106" t="n">
         <v>422</v>
       </c>
-      <c r="C106" t="n">
-        <v>0</v>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -1615,8 +1824,10 @@
       <c r="B107" t="n">
         <v>430.8</v>
       </c>
-      <c r="C107" t="n">
-        <v>0</v>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -1626,8 +1837,10 @@
       <c r="B108" t="n">
         <v>433.5</v>
       </c>
-      <c r="C108" t="n">
-        <v>0</v>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -1637,8 +1850,10 @@
       <c r="B109" t="n">
         <v>434</v>
       </c>
-      <c r="C109" t="n">
-        <v>0</v>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -1648,8 +1863,10 @@
       <c r="B110" t="n">
         <v>431</v>
       </c>
-      <c r="C110" t="n">
-        <v>0</v>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -1659,8 +1876,10 @@
       <c r="B111" t="n">
         <v>437</v>
       </c>
-      <c r="C111" t="n">
-        <v>0</v>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -1670,8 +1889,10 @@
       <c r="B112" t="n">
         <v>458</v>
       </c>
-      <c r="C112" t="n">
-        <v>0</v>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -1681,8 +1902,10 @@
       <c r="B113" t="n">
         <v>480.9</v>
       </c>
-      <c r="C113" t="n">
-        <v>1</v>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -1692,8 +1915,10 @@
       <c r="B114" t="n">
         <v>514</v>
       </c>
-      <c r="C114" t="n">
-        <v>1</v>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -1703,8 +1928,10 @@
       <c r="B115" t="n">
         <v>517</v>
       </c>
-      <c r="C115" t="n">
-        <v>1</v>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -1714,8 +1941,10 @@
       <c r="B116" t="n">
         <v>507.9</v>
       </c>
-      <c r="C116" t="n">
-        <v>1</v>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -1725,8 +1954,10 @@
       <c r="B117" t="n">
         <v>489</v>
       </c>
-      <c r="C117" t="n">
-        <v>1</v>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -1736,8 +1967,10 @@
       <c r="B118" t="n">
         <v>478.3</v>
       </c>
-      <c r="C118" t="n">
-        <v>1</v>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -1747,8 +1980,10 @@
       <c r="B119" t="n">
         <v>490</v>
       </c>
-      <c r="C119" t="n">
-        <v>1</v>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -1758,8 +1993,10 @@
       <c r="B120" t="n">
         <v>484.9</v>
       </c>
-      <c r="C120" t="n">
-        <v>1</v>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -1769,8 +2006,10 @@
       <c r="B121" t="n">
         <v>483</v>
       </c>
-      <c r="C121" t="n">
-        <v>1</v>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -1780,8 +2019,10 @@
       <c r="B122" t="n">
         <v>480</v>
       </c>
-      <c r="C122" t="n">
-        <v>1</v>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -1791,8 +2032,10 @@
       <c r="B123" t="n">
         <v>477</v>
       </c>
-      <c r="C123" t="n">
-        <v>1</v>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -1802,8 +2045,10 @@
       <c r="B124" t="n">
         <v>474</v>
       </c>
-      <c r="C124" t="n">
-        <v>1</v>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -1813,8 +2058,10 @@
       <c r="B125" t="n">
         <v>468</v>
       </c>
-      <c r="C125" t="n">
-        <v>1</v>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -1824,8 +2071,10 @@
       <c r="B126" t="n">
         <v>478</v>
       </c>
-      <c r="C126" t="n">
-        <v>1</v>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -1835,8 +2084,10 @@
       <c r="B127" t="n">
         <v>483</v>
       </c>
-      <c r="C127" t="n">
-        <v>1</v>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -1846,8 +2097,10 @@
       <c r="B128" t="n">
         <v>479.1</v>
       </c>
-      <c r="C128" t="n">
-        <v>1</v>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -1857,8 +2110,10 @@
       <c r="B129" t="n">
         <v>475</v>
       </c>
-      <c r="C129" t="n">
-        <v>1</v>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -1868,8 +2123,10 @@
       <c r="B130" t="n">
         <v>469</v>
       </c>
-      <c r="C130" t="n">
-        <v>1</v>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -1879,8 +2136,10 @@
       <c r="B131" t="n">
         <v>472</v>
       </c>
-      <c r="C131" t="n">
-        <v>1</v>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -1890,8 +2149,10 @@
       <c r="B132" t="n">
         <v>470.1</v>
       </c>
-      <c r="C132" t="n">
-        <v>1</v>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -1901,8 +2162,10 @@
       <c r="B133" t="n">
         <v>466</v>
       </c>
-      <c r="C133" t="n">
-        <v>1</v>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -1912,8 +2175,10 @@
       <c r="B134" t="n">
         <v>461.1</v>
       </c>
-      <c r="C134" t="n">
-        <v>1</v>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -1923,8 +2188,10 @@
       <c r="B135" t="n">
         <v>458.2</v>
       </c>
-      <c r="C135" t="n">
-        <v>1</v>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -1934,8 +2201,10 @@
       <c r="B136" t="n">
         <v>456</v>
       </c>
-      <c r="C136" t="n">
-        <v>1</v>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -1945,8 +2214,10 @@
       <c r="B137" t="n">
         <v>456</v>
       </c>
-      <c r="C137" t="n">
-        <v>1</v>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -1956,8 +2227,10 @@
       <c r="B138" t="n">
         <v>452</v>
       </c>
-      <c r="C138" t="n">
-        <v>1</v>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -1967,8 +2240,10 @@
       <c r="B139" t="n">
         <v>458.8</v>
       </c>
-      <c r="C139" t="n">
-        <v>1</v>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -1978,8 +2253,10 @@
       <c r="B140" t="n">
         <v>477.1</v>
       </c>
-      <c r="C140" t="n">
-        <v>1</v>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -1989,8 +2266,10 @@
       <c r="B141" t="n">
         <v>484</v>
       </c>
-      <c r="C141" t="n">
-        <v>1</v>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -2000,8 +2279,10 @@
       <c r="B142" t="n">
         <v>487</v>
       </c>
-      <c r="C142" t="n">
-        <v>1</v>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -2011,8 +2292,10 @@
       <c r="B143" t="n">
         <v>487</v>
       </c>
-      <c r="C143" t="n">
-        <v>1</v>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -2022,8 +2305,10 @@
       <c r="B144" t="n">
         <v>490</v>
       </c>
-      <c r="C144" t="n">
-        <v>1</v>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -2033,8 +2318,10 @@
       <c r="B145" t="n">
         <v>490.2</v>
       </c>
-      <c r="C145" t="n">
-        <v>1</v>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -2044,8 +2331,10 @@
       <c r="B146" t="n">
         <v>497.1</v>
       </c>
-      <c r="C146" t="n">
-        <v>1</v>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -2055,8 +2344,10 @@
       <c r="B147" t="n">
         <v>507</v>
       </c>
-      <c r="C147" t="n">
-        <v>1</v>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -2066,8 +2357,10 @@
       <c r="B148" t="n">
         <v>529</v>
       </c>
-      <c r="C148" t="n">
-        <v>1</v>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -2077,8 +2370,10 @@
       <c r="B149" t="n">
         <v>524</v>
       </c>
-      <c r="C149" t="n">
-        <v>1</v>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -2088,8 +2383,10 @@
       <c r="B150" t="n">
         <v>532.9</v>
       </c>
-      <c r="C150" t="n">
-        <v>1</v>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -2099,8 +2396,10 @@
       <c r="B151" t="n">
         <v>538</v>
       </c>
-      <c r="C151" t="n">
-        <v>1</v>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -2110,8 +2409,10 @@
       <c r="B152" t="n">
         <v>567</v>
       </c>
-      <c r="C152" t="n">
-        <v>0</v>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -2121,8 +2422,10 @@
       <c r="B153" t="n">
         <v>577</v>
       </c>
-      <c r="C153" t="n">
-        <v>0</v>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -2132,8 +2435,10 @@
       <c r="B154" t="n">
         <v>574</v>
       </c>
-      <c r="C154" t="n">
-        <v>0</v>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -2143,8 +2448,10 @@
       <c r="B155" t="n">
         <v>579</v>
       </c>
-      <c r="C155" t="n">
-        <v>1</v>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -2154,8 +2461,10 @@
       <c r="B156" t="n">
         <v>579</v>
       </c>
-      <c r="C156" t="n">
-        <v>1</v>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -2165,8 +2474,10 @@
       <c r="B157" t="n">
         <v>575.9</v>
       </c>
-      <c r="C157" t="n">
-        <v>1</v>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -2176,8 +2487,10 @@
       <c r="B158" t="n">
         <v>633.4</v>
       </c>
-      <c r="C158" t="n">
-        <v>0</v>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -2187,8 +2500,10 @@
       <c r="B159" t="n">
         <v>649</v>
       </c>
-      <c r="C159" t="n">
-        <v>0</v>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -2198,8 +2513,10 @@
       <c r="B160" t="n">
         <v>644</v>
       </c>
-      <c r="C160" t="n">
-        <v>1</v>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -2209,8 +2526,10 @@
       <c r="B161" t="n">
         <v>649.3</v>
       </c>
-      <c r="C161" t="n">
-        <v>0</v>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -2220,8 +2539,10 @@
       <c r="B162" t="n">
         <v>645</v>
       </c>
-      <c r="C162" t="n">
-        <v>1</v>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -2231,8 +2552,10 @@
       <c r="B163" t="n">
         <v>660</v>
       </c>
-      <c r="C163" t="n">
-        <v>1</v>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -2242,8 +2565,10 @@
       <c r="B164" t="n">
         <v>625</v>
       </c>
-      <c r="C164" t="n">
-        <v>1</v>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -2253,8 +2578,10 @@
       <c r="B165" t="n">
         <v>631.5</v>
       </c>
-      <c r="C165" t="n">
-        <v>0</v>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -2264,8 +2591,10 @@
       <c r="B166" t="n">
         <v>630</v>
       </c>
-      <c r="C166" t="n">
-        <v>0</v>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -2275,8 +2604,10 @@
       <c r="B167" t="n">
         <v>639.1</v>
       </c>
-      <c r="C167" t="n">
-        <v>0</v>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -2286,8 +2617,10 @@
       <c r="B168" t="n">
         <v>646.9</v>
       </c>
-      <c r="C168" t="n">
-        <v>0</v>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -2297,8 +2630,10 @@
       <c r="B169" t="n">
         <v>647.9</v>
       </c>
-      <c r="C169" t="n">
-        <v>0</v>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -2308,8 +2643,10 @@
       <c r="B170" t="n">
         <v>645</v>
       </c>
-      <c r="C170" t="n">
-        <v>1</v>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -2319,8 +2656,10 @@
       <c r="B171" t="n">
         <v>660</v>
       </c>
-      <c r="C171" t="n">
-        <v>0</v>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -2330,8 +2669,10 @@
       <c r="B172" t="n">
         <v>662</v>
       </c>
-      <c r="C172" t="n">
-        <v>1</v>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -2341,8 +2682,10 @@
       <c r="B173" t="n">
         <v>658.3</v>
       </c>
-      <c r="C173" t="n">
-        <v>1</v>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -2352,8 +2695,10 @@
       <c r="B174" t="n">
         <v>654</v>
       </c>
-      <c r="C174" t="n">
-        <v>1</v>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -2363,8 +2708,10 @@
       <c r="B175" t="n">
         <v>636.9</v>
       </c>
-      <c r="C175" t="n">
-        <v>1</v>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -2374,8 +2721,10 @@
       <c r="B176" t="n">
         <v>605.6</v>
       </c>
-      <c r="C176" t="n">
-        <v>1</v>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -2385,8 +2734,10 @@
       <c r="B177" t="n">
         <v>616</v>
       </c>
-      <c r="C177" t="n">
-        <v>1</v>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -2396,8 +2747,10 @@
       <c r="B178" t="n">
         <v>605</v>
       </c>
-      <c r="C178" t="n">
-        <v>1</v>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -2407,8 +2760,10 @@
       <c r="B179" t="n">
         <v>595</v>
       </c>
-      <c r="C179" t="n">
-        <v>1</v>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -2418,8 +2773,10 @@
       <c r="B180" t="n">
         <v>611.7</v>
       </c>
-      <c r="C180" t="n">
-        <v>1</v>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -2429,8 +2786,10 @@
       <c r="B181" t="n">
         <v>610</v>
       </c>
-      <c r="C181" t="n">
-        <v>1</v>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -2440,8 +2799,10 @@
       <c r="B182" t="n">
         <v>595</v>
       </c>
-      <c r="C182" t="n">
-        <v>1</v>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -2451,8 +2812,10 @@
       <c r="B183" t="n">
         <v>592</v>
       </c>
-      <c r="C183" t="n">
-        <v>1</v>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -2462,8 +2825,10 @@
       <c r="B184" t="n">
         <v>586</v>
       </c>
-      <c r="C184" t="n">
-        <v>1</v>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -2473,8 +2838,10 @@
       <c r="B185" t="n">
         <v>573</v>
       </c>
-      <c r="C185" t="n">
-        <v>1</v>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -2484,8 +2851,10 @@
       <c r="B186" t="n">
         <v>569.8</v>
       </c>
-      <c r="C186" t="n">
-        <v>1</v>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -2495,8 +2864,10 @@
       <c r="B187" t="n">
         <v>561.5</v>
       </c>
-      <c r="C187" t="n">
-        <v>1</v>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -2506,8 +2877,10 @@
       <c r="B188" t="n">
         <v>569</v>
       </c>
-      <c r="C188" t="n">
-        <v>1</v>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -2517,8 +2890,10 @@
       <c r="B189" t="n">
         <v>571</v>
       </c>
-      <c r="C189" t="n">
-        <v>1</v>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -2528,8 +2903,10 @@
       <c r="B190" t="n">
         <v>561.2</v>
       </c>
-      <c r="C190" t="n">
-        <v>1</v>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -2539,8 +2916,10 @@
       <c r="B191" t="n">
         <v>556</v>
       </c>
-      <c r="C191" t="n">
-        <v>1</v>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -2550,8 +2929,10 @@
       <c r="B192" t="n">
         <v>562</v>
       </c>
-      <c r="C192" t="n">
-        <v>1</v>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -2561,8 +2942,10 @@
       <c r="B193" t="n">
         <v>568</v>
       </c>
-      <c r="C193" t="n">
-        <v>1</v>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -2572,8 +2955,10 @@
       <c r="B194" t="n">
         <v>553.5</v>
       </c>
-      <c r="C194" t="n">
-        <v>1</v>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -2583,8 +2968,10 @@
       <c r="B195" t="n">
         <v>555</v>
       </c>
-      <c r="C195" t="n">
-        <v>1</v>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -2594,8 +2981,10 @@
       <c r="B196" t="n">
         <v>550</v>
       </c>
-      <c r="C196" t="n">
-        <v>1</v>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -2605,8 +2994,10 @@
       <c r="B197" t="n">
         <v>541.5</v>
       </c>
-      <c r="C197" t="n">
-        <v>1</v>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -2616,8 +3007,10 @@
       <c r="B198" t="n">
         <v>550</v>
       </c>
-      <c r="C198" t="n">
-        <v>1</v>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -2627,8 +3020,10 @@
       <c r="B199" t="n">
         <v>568</v>
       </c>
-      <c r="C199" t="n">
-        <v>1</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -2638,8 +3033,10 @@
       <c r="B200" t="n">
         <v>565</v>
       </c>
-      <c r="C200" t="n">
-        <v>1</v>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -2649,8 +3046,10 @@
       <c r="B201" t="n">
         <v>574</v>
       </c>
-      <c r="C201" t="n">
-        <v>1</v>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -2660,8 +3059,10 @@
       <c r="B202" t="n">
         <v>591.5</v>
       </c>
-      <c r="C202" t="n">
-        <v>1</v>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -2671,8 +3072,10 @@
       <c r="B203" t="n">
         <v>591</v>
       </c>
-      <c r="C203" t="n">
-        <v>1</v>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -2682,8 +3085,10 @@
       <c r="B204" t="n">
         <v>593</v>
       </c>
-      <c r="C204" t="n">
-        <v>1</v>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -2693,8 +3098,10 @@
       <c r="B205" t="n">
         <v>600</v>
       </c>
-      <c r="C205" t="n">
-        <v>1</v>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -2704,8 +3111,10 @@
       <c r="B206" t="n">
         <v>608</v>
       </c>
-      <c r="C206" t="n">
-        <v>0</v>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -2715,8 +3124,10 @@
       <c r="B207" t="n">
         <v>607.1</v>
       </c>
-      <c r="C207" t="n">
-        <v>0</v>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -2726,8 +3137,10 @@
       <c r="B208" t="n">
         <v>597</v>
       </c>
-      <c r="C208" t="n">
-        <v>0</v>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -2737,8 +3150,10 @@
       <c r="B209" t="n">
         <v>585.5</v>
       </c>
-      <c r="C209" t="n">
-        <v>0</v>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -2748,8 +3163,10 @@
       <c r="B210" t="n">
         <v>591</v>
       </c>
-      <c r="C210" t="n">
-        <v>0</v>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -2759,8 +3176,10 @@
       <c r="B211" t="n">
         <v>594</v>
       </c>
-      <c r="C211" t="n">
-        <v>0</v>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -2770,8 +3189,10 @@
       <c r="B212" t="n">
         <v>591.5</v>
       </c>
-      <c r="C212" t="n">
-        <v>0</v>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -2781,8 +3202,10 @@
       <c r="B213" t="n">
         <v>587</v>
       </c>
-      <c r="C213" t="n">
-        <v>0</v>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -2792,8 +3215,10 @@
       <c r="B214" t="n">
         <v>585</v>
       </c>
-      <c r="C214" t="n">
-        <v>0</v>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -2803,8 +3228,10 @@
       <c r="B215" t="n">
         <v>591.8</v>
       </c>
-      <c r="C215" t="n">
-        <v>0</v>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -2814,8 +3241,10 @@
       <c r="B216" t="n">
         <v>576</v>
       </c>
-      <c r="C216" t="n">
-        <v>0</v>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -2825,8 +3254,10 @@
       <c r="B217" t="n">
         <v>567</v>
       </c>
-      <c r="C217" t="n">
-        <v>0</v>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -2836,8 +3267,10 @@
       <c r="B218" t="n">
         <v>564.6</v>
       </c>
-      <c r="C218" t="n">
-        <v>0</v>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -2847,8 +3280,10 @@
       <c r="B219" t="n">
         <v>570</v>
       </c>
-      <c r="C219" t="n">
-        <v>0</v>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -2858,8 +3293,10 @@
       <c r="B220" t="n">
         <v>569</v>
       </c>
-      <c r="C220" t="n">
-        <v>0</v>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -2869,8 +3306,10 @@
       <c r="B221" t="n">
         <v>566.2</v>
       </c>
-      <c r="C221" t="n">
-        <v>0</v>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -2880,8 +3319,10 @@
       <c r="B222" t="n">
         <v>561</v>
       </c>
-      <c r="C222" t="n">
-        <v>0</v>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -2891,8 +3332,10 @@
       <c r="B223" t="n">
         <v>562</v>
       </c>
-      <c r="C223" t="n">
-        <v>0</v>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -2902,8 +3345,10 @@
       <c r="B224" t="n">
         <v>562.1</v>
       </c>
-      <c r="C224" t="n">
-        <v>0</v>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -2913,8 +3358,10 @@
       <c r="B225" t="n">
         <v>559.8</v>
       </c>
-      <c r="C225" t="n">
-        <v>0</v>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -2924,8 +3371,10 @@
       <c r="B226" t="n">
         <v>557</v>
       </c>
-      <c r="C226" t="n">
-        <v>0</v>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -2935,8 +3384,10 @@
       <c r="B227" t="n">
         <v>553.7</v>
       </c>
-      <c r="C227" t="n">
-        <v>0</v>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -2946,8 +3397,10 @@
       <c r="B228" t="n">
         <v>558</v>
       </c>
-      <c r="C228" t="n">
-        <v>0</v>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -2957,8 +3410,10 @@
       <c r="B229" t="n">
         <v>547.6</v>
       </c>
-      <c r="C229" t="n">
-        <v>0</v>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -2968,8 +3423,10 @@
       <c r="B230" t="n">
         <v>545</v>
       </c>
-      <c r="C230" t="n">
-        <v>0</v>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -2979,8 +3436,10 @@
       <c r="B231" t="n">
         <v>548</v>
       </c>
-      <c r="C231" t="n">
-        <v>0</v>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -2990,8 +3449,10 @@
       <c r="B232" t="n">
         <v>540</v>
       </c>
-      <c r="C232" t="n">
-        <v>0</v>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -3001,8 +3462,10 @@
       <c r="B233" t="n">
         <v>536</v>
       </c>
-      <c r="C233" t="n">
-        <v>0</v>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -3012,8 +3475,10 @@
       <c r="B234" t="n">
         <v>534</v>
       </c>
-      <c r="C234" t="n">
-        <v>0</v>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -3023,8 +3488,10 @@
       <c r="B235" t="n">
         <v>532</v>
       </c>
-      <c r="C235" t="n">
-        <v>0</v>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -3034,8 +3501,10 @@
       <c r="B236" t="n">
         <v>530</v>
       </c>
-      <c r="C236" t="n">
-        <v>1</v>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -3045,8 +3514,10 @@
       <c r="B237" t="n">
         <v>525</v>
       </c>
-      <c r="C237" t="n">
-        <v>1</v>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -3056,8 +3527,10 @@
       <c r="B238" t="n">
         <v>514.5</v>
       </c>
-      <c r="C238" t="n">
-        <v>1</v>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -3067,8 +3540,10 @@
       <c r="B239" t="n">
         <v>510</v>
       </c>
-      <c r="C239" t="n">
-        <v>1</v>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -3078,8 +3553,10 @@
       <c r="B240" t="n">
         <v>508.1</v>
       </c>
-      <c r="C240" t="n">
-        <v>1</v>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -3089,8 +3566,10 @@
       <c r="B241" t="n">
         <v>528</v>
       </c>
-      <c r="C241" t="n">
-        <v>1</v>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -3100,8 +3579,10 @@
       <c r="B242" t="n">
         <v>520</v>
       </c>
-      <c r="C242" t="n">
-        <v>1</v>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -3111,8 +3592,10 @@
       <c r="B243" t="n">
         <v>512.9</v>
       </c>
-      <c r="C243" t="n">
-        <v>1</v>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -3122,8 +3605,10 @@
       <c r="B244" t="n">
         <v>512</v>
       </c>
-      <c r="C244" t="n">
-        <v>1</v>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -3133,8 +3618,10 @@
       <c r="B245" t="n">
         <v>511.8</v>
       </c>
-      <c r="C245" t="n">
-        <v>1</v>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -3144,8 +3631,10 @@
       <c r="B246" t="n">
         <v>508</v>
       </c>
-      <c r="C246" t="n">
-        <v>1</v>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -3155,8 +3644,10 @@
       <c r="B247" t="n">
         <v>502.9</v>
       </c>
-      <c r="C247" t="n">
-        <v>1</v>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -3166,8 +3657,10 @@
       <c r="B248" t="n">
         <v>501</v>
       </c>
-      <c r="C248" t="n">
-        <v>1</v>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -3177,8 +3670,10 @@
       <c r="B249" t="n">
         <v>501</v>
       </c>
-      <c r="C249" t="n">
-        <v>1</v>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -3188,8 +3683,10 @@
       <c r="B250" t="n">
         <v>502</v>
       </c>
-      <c r="C250" t="n">
-        <v>1</v>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -3199,8 +3696,10 @@
       <c r="B251" t="n">
         <v>502.7</v>
       </c>
-      <c r="C251" t="n">
-        <v>1</v>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -3210,8 +3709,10 @@
       <c r="B252" t="n">
         <v>502</v>
       </c>
-      <c r="C252" t="n">
-        <v>1</v>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -3221,8 +3722,10 @@
       <c r="B253" t="n">
         <v>501.4</v>
       </c>
-      <c r="C253" t="n">
-        <v>1</v>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -3232,8 +3735,10 @@
       <c r="B254" t="n">
         <v>499.3</v>
       </c>
-      <c r="C254" t="n">
-        <v>1</v>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -3243,8 +3748,10 @@
       <c r="B255" t="n">
         <v>499</v>
       </c>
-      <c r="C255" t="n">
-        <v>1</v>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -3254,8 +3761,10 @@
       <c r="B256" t="n">
         <v>499</v>
       </c>
-      <c r="C256" t="n">
-        <v>1</v>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -3265,8 +3774,10 @@
       <c r="B257" t="n">
         <v>500</v>
       </c>
-      <c r="C257" t="n">
-        <v>1</v>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -3276,8 +3787,10 @@
       <c r="B258" t="n">
         <v>498.9</v>
       </c>
-      <c r="C258" t="n">
-        <v>0</v>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -3287,8 +3800,10 @@
       <c r="B259" t="n">
         <v>495.5</v>
       </c>
-      <c r="C259" t="n">
-        <v>0</v>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -3298,8 +3813,10 @@
       <c r="B260" t="n">
         <v>490.6</v>
       </c>
-      <c r="C260" t="n">
-        <v>0</v>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -3309,8 +3826,10 @@
       <c r="B261" t="n">
         <v>489.5</v>
       </c>
-      <c r="C261" t="n">
-        <v>1</v>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -3320,8 +3839,10 @@
       <c r="B262" t="n">
         <v>489.5</v>
       </c>
-      <c r="C262" t="n">
-        <v>0</v>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -3331,8 +3852,10 @@
       <c r="B263" t="n">
         <v>489.1</v>
       </c>
-      <c r="C263" t="n">
-        <v>0</v>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -3342,8 +3865,10 @@
       <c r="B264" t="n">
         <v>488.2</v>
       </c>
-      <c r="C264" t="n">
-        <v>0</v>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -3353,8 +3878,10 @@
       <c r="B265" t="n">
         <v>484.5</v>
       </c>
-      <c r="C265" t="n">
-        <v>0</v>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -3364,8 +3891,10 @@
       <c r="B266" t="n">
         <v>483.4</v>
       </c>
-      <c r="C266" t="n">
-        <v>0</v>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -3375,8 +3904,10 @@
       <c r="B267" t="n">
         <v>486</v>
       </c>
-      <c r="C267" t="n">
-        <v>0</v>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -3386,8 +3917,10 @@
       <c r="B268" t="n">
         <v>488</v>
       </c>
-      <c r="C268" t="n">
-        <v>0</v>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -3397,8 +3930,10 @@
       <c r="B269" t="n">
         <v>482.2</v>
       </c>
-      <c r="C269" t="n">
-        <v>0</v>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -3408,8 +3943,10 @@
       <c r="B270" t="n">
         <v>479.5</v>
       </c>
-      <c r="C270" t="n">
-        <v>0</v>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -3419,8 +3956,10 @@
       <c r="B271" t="n">
         <v>476</v>
       </c>
-      <c r="C271" t="n">
-        <v>0</v>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -3430,8 +3969,10 @@
       <c r="B272" t="n">
         <v>491.4</v>
       </c>
-      <c r="C272" t="n">
-        <v>1</v>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -3441,8 +3982,10 @@
       <c r="B273" t="n">
         <v>495.9</v>
       </c>
-      <c r="C273" t="n">
-        <v>0</v>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -3452,8 +3995,10 @@
       <c r="B274" t="n">
         <v>493</v>
       </c>
-      <c r="C274" t="n">
-        <v>0</v>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -3463,8 +4008,10 @@
       <c r="B275" t="n">
         <v>490</v>
       </c>
-      <c r="C275" t="n">
-        <v>0</v>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -3474,8 +4021,10 @@
       <c r="B276" t="n">
         <v>486.7</v>
       </c>
-      <c r="C276" t="n">
-        <v>0</v>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -3485,8 +4034,10 @@
       <c r="B277" t="n">
         <v>486.3</v>
       </c>
-      <c r="C277" t="n">
-        <v>0</v>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -3496,8 +4047,10 @@
       <c r="B278" t="n">
         <v>490</v>
       </c>
-      <c r="C278" t="n">
-        <v>0</v>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -3507,8 +4060,10 @@
       <c r="B279" t="n">
         <v>487</v>
       </c>
-      <c r="C279" t="n">
-        <v>0</v>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -3518,8 +4073,10 @@
       <c r="B280" t="n">
         <v>485</v>
       </c>
-      <c r="C280" t="n">
-        <v>0</v>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -3529,8 +4086,10 @@
       <c r="B281" t="n">
         <v>485.5</v>
       </c>
-      <c r="C281" t="n">
-        <v>0</v>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -3540,8 +4099,10 @@
       <c r="B282" t="n">
         <v>487</v>
       </c>
-      <c r="C282" t="n">
-        <v>0</v>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -3551,8 +4112,10 @@
       <c r="B283" t="n">
         <v>494</v>
       </c>
-      <c r="C283" t="n">
-        <v>0</v>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -3562,8 +4125,10 @@
       <c r="B284" t="n">
         <v>496</v>
       </c>
-      <c r="C284" t="n">
-        <v>0</v>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -3573,8 +4138,10 @@
       <c r="B285" t="n">
         <v>494.9</v>
       </c>
-      <c r="C285" t="n">
-        <v>0</v>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -3584,8 +4151,10 @@
       <c r="B286" t="n">
         <v>489.9</v>
       </c>
-      <c r="C286" t="n">
-        <v>0</v>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -3595,8 +4164,10 @@
       <c r="B287" t="n">
         <v>489</v>
       </c>
-      <c r="C287" t="n">
-        <v>0</v>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -3606,8 +4177,10 @@
       <c r="B288" t="n">
         <v>489</v>
       </c>
-      <c r="C288" t="n">
-        <v>0</v>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -3617,8 +4190,10 @@
       <c r="B289" t="n">
         <v>501.8</v>
       </c>
-      <c r="C289" t="n">
-        <v>0</v>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -3628,8 +4203,10 @@
       <c r="B290" t="n">
         <v>519</v>
       </c>
-      <c r="C290" t="n">
-        <v>0</v>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -3639,8 +4216,10 @@
       <c r="B291" t="n">
         <v>515</v>
       </c>
-      <c r="C291" t="n">
-        <v>0</v>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -3650,8 +4229,10 @@
       <c r="B292" t="n">
         <v>507</v>
       </c>
-      <c r="C292" t="n">
-        <v>1</v>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -3661,8 +4242,10 @@
       <c r="B293" t="n">
         <v>499</v>
       </c>
-      <c r="C293" t="n">
-        <v>1</v>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -3672,8 +4255,10 @@
       <c r="B294" t="n">
         <v>498.1</v>
       </c>
-      <c r="C294" t="n">
-        <v>1</v>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -3683,8 +4268,10 @@
       <c r="B295" t="n">
         <v>495</v>
       </c>
-      <c r="C295" t="n">
-        <v>1</v>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -3694,8 +4281,10 @@
       <c r="B296" t="n">
         <v>491</v>
       </c>
-      <c r="C296" t="n">
-        <v>1</v>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -3705,8 +4294,10 @@
       <c r="B297" t="n">
         <v>491</v>
       </c>
-      <c r="C297" t="n">
-        <v>1</v>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -3716,8 +4307,10 @@
       <c r="B298" t="n">
         <v>491</v>
       </c>
-      <c r="C298" t="n">
-        <v>1</v>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -3727,8 +4320,10 @@
       <c r="B299" t="n">
         <v>491.1</v>
       </c>
-      <c r="C299" t="n">
-        <v>0</v>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -3738,8 +4333,10 @@
       <c r="B300" t="n">
         <v>490</v>
       </c>
-      <c r="C300" t="n">
-        <v>0</v>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="301">
@@ -3749,8 +4346,10 @@
       <c r="B301" t="n">
         <v>491.4</v>
       </c>
-      <c r="C301" t="n">
-        <v>0</v>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="302">
@@ -3760,8 +4359,10 @@
       <c r="B302" t="n">
         <v>488.9</v>
       </c>
-      <c r="C302" t="n">
-        <v>0</v>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="303">
@@ -3771,8 +4372,10 @@
       <c r="B303" t="n">
         <v>487.31</v>
       </c>
-      <c r="C303" t="n">
-        <v>0</v>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="304">
@@ -3782,8 +4385,10 @@
       <c r="B304" t="n">
         <v>482.62</v>
       </c>
-      <c r="C304" t="n">
-        <v>1</v>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="305">
@@ -3793,8 +4398,10 @@
       <c r="B305" t="n">
         <v>484.03</v>
       </c>
-      <c r="C305" t="n">
-        <v>0</v>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="306">
@@ -3804,8 +4411,10 @@
       <c r="B306" t="n">
         <v>480.13</v>
       </c>
-      <c r="C306" t="n">
-        <v>0</v>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="307">
@@ -3815,8 +4424,10 @@
       <c r="B307" t="n">
         <v>481.31</v>
       </c>
-      <c r="C307" t="n">
-        <v>0</v>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="308">
@@ -3826,8 +4437,10 @@
       <c r="B308" t="n">
         <v>485.09</v>
       </c>
-      <c r="C308" t="n">
-        <v>0</v>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="309">
@@ -3837,8 +4450,10 @@
       <c r="B309" t="n">
         <v>485.96</v>
       </c>
-      <c r="C309" t="n">
-        <v>0</v>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="310">
@@ -3848,8 +4463,10 @@
       <c r="B310" t="n">
         <v>484.56</v>
       </c>
-      <c r="C310" t="n">
-        <v>0</v>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="311">
@@ -3859,8 +4476,10 @@
       <c r="B311" t="n">
         <v>485.26</v>
       </c>
-      <c r="C311" t="n">
-        <v>0</v>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="312">
@@ -3870,8 +4489,10 @@
       <c r="B312" t="n">
         <v>488.73</v>
       </c>
-      <c r="C312" t="n">
-        <v>0</v>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="313">
@@ -3881,8 +4502,10 @@
       <c r="B313" t="n">
         <v>486.97</v>
       </c>
-      <c r="C313" t="n">
-        <v>0</v>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="314">
@@ -3892,8 +4515,10 @@
       <c r="B314" t="n">
         <v>484.65</v>
       </c>
-      <c r="C314" t="n">
-        <v>0</v>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="315">
@@ -3903,8 +4528,10 @@
       <c r="B315" t="n">
         <v>486.27</v>
       </c>
-      <c r="C315" t="n">
-        <v>0</v>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="316">
@@ -3914,8 +4541,10 @@
       <c r="B316" t="n">
         <v>485.97</v>
       </c>
-      <c r="C316" t="n">
-        <v>0</v>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="317">
@@ -3925,8 +4554,10 @@
       <c r="B317" t="n">
         <v>486.97</v>
       </c>
-      <c r="C317" t="n">
-        <v>0</v>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="318">
@@ -3936,8 +4567,10 @@
       <c r="B318" t="n">
         <v>487.96</v>
       </c>
-      <c r="C318" t="n">
-        <v>0</v>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="319">
@@ -3947,8 +4580,10 @@
       <c r="B319" t="n">
         <v>489.31</v>
       </c>
-      <c r="C319" t="n">
-        <v>0</v>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="320">
@@ -3958,8 +4593,10 @@
       <c r="B320" t="n">
         <v>494.38</v>
       </c>
-      <c r="C320" t="n">
-        <v>0</v>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="321">
@@ -3969,8 +4606,10 @@
       <c r="B321" t="n">
         <v>492.09</v>
       </c>
-      <c r="C321" t="n">
-        <v>0</v>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="322">
@@ -3980,8 +4619,10 @@
       <c r="B322" t="n">
         <v>490.87</v>
       </c>
-      <c r="C322" t="n">
-        <v>0</v>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="323">
@@ -3991,8 +4632,10 @@
       <c r="B323" t="n">
         <v>487.76</v>
       </c>
-      <c r="C323" t="n">
-        <v>0</v>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="324">
@@ -4002,8 +4645,10 @@
       <c r="B324" t="n">
         <v>486.77</v>
       </c>
-      <c r="C324" t="n">
-        <v>0</v>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="325">
@@ -4013,8 +4658,10 @@
       <c r="B325" t="n">
         <v>485.87</v>
       </c>
-      <c r="C325" t="n">
-        <v>0</v>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="326">
@@ -4024,8 +4671,10 @@
       <c r="B326" t="n">
         <v>485.01</v>
       </c>
-      <c r="C326" t="n">
-        <v>0</v>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="327">
@@ -4035,8 +4684,10 @@
       <c r="B327" t="n">
         <v>481.3</v>
       </c>
-      <c r="C327" t="n">
-        <v>0</v>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="328">
@@ -4046,8 +4697,10 @@
       <c r="B328" t="n">
         <v>481.45</v>
       </c>
-      <c r="C328" t="n">
-        <v>0</v>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="329">
@@ -4057,8 +4710,10 @@
       <c r="B329" t="n">
         <v>478.18</v>
       </c>
-      <c r="C329" t="n">
-        <v>0</v>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="330">
@@ -4068,8 +4723,10 @@
       <c r="B330" t="n">
         <v>478.32</v>
       </c>
-      <c r="C330" t="n">
-        <v>0</v>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="331">
@@ -4079,8 +4736,10 @@
       <c r="B331" t="n">
         <v>478.25</v>
       </c>
-      <c r="C331" t="n">
-        <v>0</v>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="332">
@@ -4090,8 +4749,10 @@
       <c r="B332" t="n">
         <v>476.94</v>
       </c>
-      <c r="C332" t="n">
-        <v>0</v>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="333">
@@ -4101,8 +4762,10 @@
       <c r="B333" t="n">
         <v>483.31</v>
       </c>
-      <c r="C333" t="n">
-        <v>0</v>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="334">
@@ -4112,8 +4775,10 @@
       <c r="B334" t="n">
         <v>482.64</v>
       </c>
-      <c r="C334" t="n">
-        <v>0</v>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="335">
@@ -4123,8 +4788,10 @@
       <c r="B335" t="n">
         <v>485.65</v>
       </c>
-      <c r="C335" t="n">
-        <v>0</v>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="336">
@@ -4134,8 +4801,10 @@
       <c r="B336" t="n">
         <v>487.41</v>
       </c>
-      <c r="C336" t="n">
-        <v>0</v>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="337">
@@ -4145,8 +4814,10 @@
       <c r="B337" t="n">
         <v>483.85</v>
       </c>
-      <c r="C337" t="n">
-        <v>0</v>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="338">
@@ -4156,8 +4827,10 @@
       <c r="B338" t="n">
         <v>482.11</v>
       </c>
-      <c r="C338" t="n">
-        <v>0</v>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="339">
@@ -4167,8 +4840,10 @@
       <c r="B339" t="n">
         <v>480.49</v>
       </c>
-      <c r="C339" t="n">
-        <v>0</v>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="340">
@@ -4178,8 +4853,10 @@
       <c r="B340" t="n">
         <v>482.58</v>
       </c>
-      <c r="C340" t="n">
-        <v>0</v>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="341">
@@ -4189,8 +4866,10 @@
       <c r="B341" t="n">
         <v>488.16</v>
       </c>
-      <c r="C341" t="n">
-        <v>0</v>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="342">
@@ -4200,8 +4879,10 @@
       <c r="B342" t="n">
         <v>494.21</v>
       </c>
-      <c r="C342" t="n">
-        <v>0</v>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="343">
@@ -4211,8 +4892,10 @@
       <c r="B343" t="n">
         <v>499.55</v>
       </c>
-      <c r="C343" t="n">
-        <v>0</v>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="344">
@@ -4222,8 +4905,10 @@
       <c r="B344" t="n">
         <v>496.75</v>
       </c>
-      <c r="C344" t="n">
-        <v>0</v>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="345">
@@ -4233,8 +4918,10 @@
       <c r="B345" t="n">
         <v>498.07</v>
       </c>
-      <c r="C345" t="n">
-        <v>0</v>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="346">
@@ -4244,8 +4931,10 @@
       <c r="B346" t="n">
         <v>496.48</v>
       </c>
-      <c r="C346" t="n">
-        <v>0</v>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="347">
@@ -4255,8 +4944,10 @@
       <c r="B347" t="n">
         <v>500.42</v>
       </c>
-      <c r="C347" t="n">
-        <v>0</v>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="348">
@@ -4266,8 +4957,10 @@
       <c r="B348" t="n">
         <v>500.78</v>
       </c>
-      <c r="C348" t="n">
-        <v>0</v>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="349">
@@ -4277,8 +4970,10 @@
       <c r="B349" t="n">
         <v>497.45</v>
       </c>
-      <c r="C349" t="n">
-        <v>0</v>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="350">
@@ -4288,8 +4983,10 @@
       <c r="B350" t="n">
         <v>491.11</v>
       </c>
-      <c r="C350" t="n">
-        <v>0</v>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="351">
@@ -4299,8 +4996,10 @@
       <c r="B351" t="n">
         <v>492.37</v>
       </c>
-      <c r="C351" t="n">
-        <v>0</v>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="352">
@@ -4310,8 +5009,10 @@
       <c r="B352" t="n">
         <v>489.65</v>
       </c>
-      <c r="C352" t="n">
-        <v>0</v>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="353">
@@ -4321,8 +5022,10 @@
       <c r="B353" t="n">
         <v>490.93</v>
       </c>
-      <c r="C353" t="n">
-        <v>0</v>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="354">
@@ -4332,8 +5035,10 @@
       <c r="B354" t="n">
         <v>491.77</v>
       </c>
-      <c r="C354" t="n">
-        <v>0</v>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="355">
@@ -4343,8 +5048,10 @@
       <c r="B355" t="n">
         <v>490.34</v>
       </c>
-      <c r="C355" t="n">
-        <v>0</v>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="356">
@@ -4354,8 +5061,10 @@
       <c r="B356" t="n">
         <v>489.44</v>
       </c>
-      <c r="C356" t="n">
-        <v>0</v>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="357">
@@ -4365,8 +5074,10 @@
       <c r="B357" t="n">
         <v>490.73</v>
       </c>
-      <c r="C357" t="n">
-        <v>0</v>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="358">
@@ -4376,8 +5087,10 @@
       <c r="B358" t="n">
         <v>490.59</v>
       </c>
-      <c r="C358" t="n">
-        <v>0</v>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="359">
@@ -4387,8 +5100,10 @@
       <c r="B359" t="n">
         <v>488.99</v>
       </c>
-      <c r="C359" t="n">
-        <v>0</v>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="360">
@@ -4398,8 +5113,10 @@
       <c r="B360" t="n">
         <v>489.97</v>
       </c>
-      <c r="C360" t="n">
-        <v>0</v>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="361">
@@ -4409,8 +5126,10 @@
       <c r="B361" t="n">
         <v>489.04</v>
       </c>
-      <c r="C361" t="n">
-        <v>0</v>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="362">
@@ -4420,8 +5139,10 @@
       <c r="B362" t="n">
         <v>488.99</v>
       </c>
-      <c r="C362" t="n">
-        <v>0</v>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="363">
@@ -4431,8 +5152,10 @@
       <c r="B363" t="n">
         <v>487.35</v>
       </c>
-      <c r="C363" t="n">
-        <v>0</v>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="364">
@@ -4442,8 +5165,10 @@
       <c r="B364" t="n">
         <v>487.3</v>
       </c>
-      <c r="C364" t="n">
-        <v>0</v>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="365">
@@ -4453,8 +5178,10 @@
       <c r="B365" t="n">
         <v>486.24</v>
       </c>
-      <c r="C365" t="n">
-        <v>0</v>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="366">
@@ -4464,8 +5191,10 @@
       <c r="B366" t="n">
         <v>485.95</v>
       </c>
-      <c r="C366" t="n">
-        <v>0</v>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="367">
@@ -4475,8 +5204,10 @@
       <c r="B367" t="n">
         <v>489.82</v>
       </c>
-      <c r="C367" t="n">
-        <v>0</v>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="368">
@@ -4486,8 +5217,10 @@
       <c r="B368" t="n">
         <v>491.81</v>
       </c>
-      <c r="C368" t="n">
-        <v>0</v>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="369">
@@ -4497,8 +5230,10 @@
       <c r="B369" t="n">
         <v>491.79</v>
       </c>
-      <c r="C369" t="n">
-        <v>0</v>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="370">
@@ -4508,8 +5243,10 @@
       <c r="B370" t="n">
         <v>494.96</v>
       </c>
-      <c r="C370" t="n">
-        <v>0</v>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="371">
@@ -4519,8 +5256,10 @@
       <c r="B371" t="n">
         <v>498.22</v>
       </c>
-      <c r="C371" t="n">
-        <v>0</v>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="372">
@@ -4530,8 +5269,10 @@
       <c r="B372" t="n">
         <v>500.89</v>
       </c>
-      <c r="C372" t="n">
-        <v>0</v>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="373">
@@ -4541,8 +5282,10 @@
       <c r="B373" t="n">
         <v>497.07</v>
       </c>
-      <c r="C373" t="n">
-        <v>0</v>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="374">
@@ -4552,8 +5295,10 @@
       <c r="B374" t="n">
         <v>495.46</v>
       </c>
-      <c r="C374" t="n">
-        <v>0</v>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="375">
@@ -4563,8 +5308,10 @@
       <c r="B375" t="n">
         <v>499.01</v>
       </c>
-      <c r="C375" t="n">
-        <v>0</v>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="376">
@@ -4574,8 +5321,10 @@
       <c r="B376" t="n">
         <v>511.17</v>
       </c>
-      <c r="C376" t="n">
-        <v>0</v>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="377">
@@ -4585,8 +5334,10 @@
       <c r="B377" t="n">
         <v>535.77</v>
       </c>
-      <c r="C377" t="n">
-        <v>0</v>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="378">
@@ -4596,8 +5347,10 @@
       <c r="B378" t="n">
         <v>522.22</v>
       </c>
-      <c r="C378" t="n">
-        <v>1</v>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="379">
@@ -4607,8 +5360,10 @@
       <c r="B379" t="n">
         <v>529.8</v>
       </c>
-      <c r="C379" t="n">
-        <v>1</v>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="380">
@@ -4618,8 +5373,10 @@
       <c r="B380" t="n">
         <v>541.37</v>
       </c>
-      <c r="C380" t="n">
-        <v>1</v>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="381">
@@ -4629,8 +5386,10 @@
       <c r="B381" t="n">
         <v>548.66</v>
       </c>
-      <c r="C381" t="n">
-        <v>1</v>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="382">
@@ -4640,8 +5399,10 @@
       <c r="B382" t="n">
         <v>549.77</v>
       </c>
-      <c r="C382" t="n">
-        <v>1</v>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="383">
@@ -4651,8 +5412,10 @@
       <c r="B383" t="n">
         <v>545.21</v>
       </c>
-      <c r="C383" t="n">
-        <v>1</v>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="384">
@@ -4662,8 +5425,10 @@
       <c r="B384" t="n">
         <v>554.63</v>
       </c>
-      <c r="C384" t="n">
-        <v>1</v>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="385">
@@ -4673,8 +5438,10 @@
       <c r="B385" t="n">
         <v>551.41</v>
       </c>
-      <c r="C385" t="n">
-        <v>1</v>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="386">
@@ -4684,8 +5451,10 @@
       <c r="B386" t="n">
         <v>548.08</v>
       </c>
-      <c r="C386" t="n">
-        <v>1</v>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="387">
@@ -4695,8 +5464,10 @@
       <c r="B387" t="n">
         <v>547.84</v>
       </c>
-      <c r="C387" t="n">
-        <v>1</v>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="388">
@@ -4706,8 +5477,10 @@
       <c r="B388" t="n">
         <v>540.4299999999999</v>
       </c>
-      <c r="C388" t="n">
-        <v>1</v>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="389">
@@ -4717,8 +5490,10 @@
       <c r="B389" t="n">
         <v>548.55</v>
       </c>
-      <c r="C389" t="n">
-        <v>1</v>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="390">
@@ -4728,8 +5503,10 @@
       <c r="B390" t="n">
         <v>545.1799999999999</v>
       </c>
-      <c r="C390" t="n">
-        <v>1</v>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="391">
@@ -4739,8 +5516,10 @@
       <c r="B391" t="n">
         <v>536.48</v>
       </c>
-      <c r="C391" t="n">
-        <v>1</v>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="392">
@@ -4750,8 +5529,10 @@
       <c r="B392" t="n">
         <v>524.4</v>
       </c>
-      <c r="C392" t="n">
-        <v>1</v>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="393">
@@ -4761,8 +5542,10 @@
       <c r="B393" t="n">
         <v>527.97</v>
       </c>
-      <c r="C393" t="n">
-        <v>1</v>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="394">
@@ -4772,8 +5555,10 @@
       <c r="B394" t="n">
         <v>527.73</v>
       </c>
-      <c r="C394" t="n">
-        <v>1</v>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="395">
@@ -4783,8 +5568,10 @@
       <c r="B395" t="n">
         <v>525.9299999999999</v>
       </c>
-      <c r="C395" t="n">
-        <v>0</v>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="396">
@@ -4794,8 +5581,10 @@
       <c r="B396" t="n">
         <v>527.36</v>
       </c>
-      <c r="C396" t="n">
-        <v>0</v>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="397">
@@ -4805,8 +5594,10 @@
       <c r="B397" t="n">
         <v>526.3</v>
       </c>
-      <c r="C397" t="n">
-        <v>0</v>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="398">
@@ -4816,8 +5607,10 @@
       <c r="B398" t="n">
         <v>524.86</v>
       </c>
-      <c r="C398" t="n">
-        <v>0</v>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="399">
@@ -4827,8 +5620,10 @@
       <c r="B399" t="n">
         <v>523.63</v>
       </c>
-      <c r="C399" t="n">
-        <v>0</v>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="400">
@@ -4838,8 +5633,10 @@
       <c r="B400" t="n">
         <v>523.8200000000001</v>
       </c>
-      <c r="C400" t="n">
-        <v>0</v>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="401">
@@ -4849,8 +5646,10 @@
       <c r="B401" t="n">
         <v>521.21</v>
       </c>
-      <c r="C401" t="n">
-        <v>0</v>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="402">
@@ -4860,8 +5659,10 @@
       <c r="B402" t="n">
         <v>518.95</v>
       </c>
-      <c r="C402" t="n">
-        <v>1</v>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="403">
@@ -4871,8 +5672,10 @@
       <c r="B403" t="n">
         <v>518.8099999999999</v>
       </c>
-      <c r="C403" t="n">
-        <v>1</v>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="404">
@@ -4882,8 +5685,10 @@
       <c r="B404" t="n">
         <v>518.8099999999999</v>
       </c>
-      <c r="C404" t="n">
-        <v>0</v>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="405">
@@ -4893,8 +5698,10 @@
       <c r="B405" t="n">
         <v>518.14</v>
       </c>
-      <c r="C405" t="n">
-        <v>0</v>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="406">
@@ -4904,8 +5711,10 @@
       <c r="B406" t="n">
         <v>513.5599999999999</v>
       </c>
-      <c r="C406" t="n">
-        <v>0</v>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="407">
@@ -4915,8 +5724,10 @@
       <c r="B407" t="n">
         <v>522.58</v>
       </c>
-      <c r="C407" t="n">
-        <v>0</v>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="408">
@@ -4926,8 +5737,10 @@
       <c r="B408" t="n">
         <v>529.35</v>
       </c>
-      <c r="C408" t="n">
-        <v>0</v>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="409">
@@ -4937,8 +5750,10 @@
       <c r="B409" t="n">
         <v>533.87</v>
       </c>
-      <c r="C409" t="n">
-        <v>0</v>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="410">
@@ -4948,8 +5763,10 @@
       <c r="B410" t="n">
         <v>528.86</v>
       </c>
-      <c r="C410" t="n">
-        <v>0</v>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="411">
@@ -4959,8 +5776,10 @@
       <c r="B411" t="n">
         <v>520.84</v>
       </c>
-      <c r="C411" t="n">
-        <v>0</v>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="412">
@@ -4970,8 +5789,10 @@
       <c r="B412" t="n">
         <v>527.66</v>
       </c>
-      <c r="C412" t="n">
-        <v>0</v>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="413">
@@ -4981,8 +5802,10 @@
       <c r="B413" t="n">
         <v>523.75</v>
       </c>
-      <c r="C413" t="n">
-        <v>0</v>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="414">
@@ -4992,8 +5815,10 @@
       <c r="B414" t="n">
         <v>519.88</v>
       </c>
-      <c r="C414" t="n">
-        <v>0</v>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="415">
@@ -5003,8 +5828,10 @@
       <c r="B415" t="n">
         <v>517.58</v>
       </c>
-      <c r="C415" t="n">
-        <v>0</v>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="416">
@@ -5014,8 +5841,10 @@
       <c r="B416" t="n">
         <v>514.87</v>
       </c>
-      <c r="C416" t="n">
-        <v>0</v>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="417">
@@ -5025,8 +5854,10 @@
       <c r="B417" t="n">
         <v>513.15</v>
       </c>
-      <c r="C417" t="n">
-        <v>0</v>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="418">
@@ -5036,8 +5867,10 @@
       <c r="B418" t="n">
         <v>483</v>
       </c>
-      <c r="C418" t="n">
-        <v>0</v>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="419">
@@ -5047,8 +5880,10 @@
       <c r="B419" t="n">
         <v>510.18</v>
       </c>
-      <c r="C419" t="n">
-        <v>0</v>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="420">
@@ -5058,8 +5893,10 @@
       <c r="B420" t="n">
         <v>523.5</v>
       </c>
-      <c r="C420" t="n">
-        <v>0</v>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="421">
@@ -5069,8 +5906,10 @@
       <c r="B421" t="n">
         <v>522</v>
       </c>
-      <c r="C421" t="n">
-        <v>0</v>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="422">
@@ -5080,8 +5919,10 @@
       <c r="B422" t="n">
         <v>521.6</v>
       </c>
-      <c r="C422" t="n">
-        <v>0</v>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="423">
@@ -5091,8 +5932,10 @@
       <c r="B423" t="n">
         <v>527</v>
       </c>
-      <c r="C423" t="n">
-        <v>0</v>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="424">
@@ -5102,8 +5945,10 @@
       <c r="B424" t="n">
         <v>521</v>
       </c>
-      <c r="C424" t="n">
-        <v>0</v>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="425">
@@ -5113,8 +5958,10 @@
       <c r="B425" t="n">
         <v>514</v>
       </c>
-      <c r="C425" t="n">
-        <v>0</v>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="426">
@@ -5124,8 +5971,10 @@
       <c r="B426" t="n">
         <v>519.9</v>
       </c>
-      <c r="C426" t="n">
-        <v>0</v>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="427">
@@ -5135,8 +5984,10 @@
       <c r="B427" t="n">
         <v>510.5</v>
       </c>
-      <c r="C427" t="n">
-        <v>0</v>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="428">
@@ -5146,8 +5997,10 @@
       <c r="B428" t="n">
         <v>510</v>
       </c>
-      <c r="C428" t="n">
-        <v>0</v>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="429">
@@ -5157,8 +6010,10 @@
       <c r="B429" t="n">
         <v>510</v>
       </c>
-      <c r="C429" t="n">
-        <v>0</v>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="430">
@@ -5168,8 +6023,10 @@
       <c r="B430" t="n">
         <v>508.7</v>
       </c>
-      <c r="C430" t="n">
-        <v>0</v>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="431">
@@ -5179,8 +6036,10 @@
       <c r="B431" t="n">
         <v>509</v>
       </c>
-      <c r="C431" t="n">
-        <v>0</v>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="432">
@@ -5190,8 +6049,10 @@
       <c r="B432" t="n">
         <v>507.9</v>
       </c>
-      <c r="C432" t="n">
-        <v>0</v>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="433">
@@ -5201,8 +6062,10 @@
       <c r="B433" t="n">
         <v>505.3</v>
       </c>
-      <c r="C433" t="n">
-        <v>1</v>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="434">
@@ -5212,8 +6075,10 @@
       <c r="B434" t="n">
         <v>509</v>
       </c>
-      <c r="C434" t="n">
-        <v>0</v>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="435">
@@ -5223,8 +6088,10 @@
       <c r="B435" t="n">
         <v>507</v>
       </c>
-      <c r="C435" t="n">
-        <v>0</v>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="436">
@@ -5234,8 +6101,10 @@
       <c r="B436" t="n">
         <v>506</v>
       </c>
-      <c r="C436" t="n">
-        <v>0</v>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="437">
@@ -5245,8 +6114,10 @@
       <c r="B437" t="n">
         <v>511.1</v>
       </c>
-      <c r="C437" t="n">
-        <v>0</v>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="438">
@@ -5256,8 +6127,10 @@
       <c r="B438" t="n">
         <v>513.1</v>
       </c>
-      <c r="C438" t="n">
-        <v>0</v>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="439">
@@ -5267,8 +6140,10 @@
       <c r="B439" t="n">
         <v>511.1</v>
       </c>
-      <c r="C439" t="n">
-        <v>0</v>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="440">
@@ -5278,8 +6153,10 @@
       <c r="B440" t="n">
         <v>513.1</v>
       </c>
-      <c r="C440" t="n">
-        <v>0</v>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="441">
@@ -5289,8 +6166,10 @@
       <c r="B441" t="n">
         <v>507.3</v>
       </c>
-      <c r="C441" t="n">
-        <v>0</v>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="442">
@@ -5300,8 +6179,10 @@
       <c r="B442" t="n">
         <v>508.5</v>
       </c>
-      <c r="C442" t="n">
-        <v>0</v>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="443">
@@ -5311,8 +6192,10 @@
       <c r="B443" t="n">
         <v>509</v>
       </c>
-      <c r="C443" t="n">
-        <v>0</v>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="444">
@@ -5322,8 +6205,10 @@
       <c r="B444" t="n">
         <v>507.9</v>
       </c>
-      <c r="C444" t="n">
-        <v>0</v>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="445">
@@ -5333,8 +6218,10 @@
       <c r="B445" t="n">
         <v>504</v>
       </c>
-      <c r="C445" t="n">
-        <v>0</v>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="446">
@@ -5344,8 +6231,10 @@
       <c r="B446" t="n">
         <v>503</v>
       </c>
-      <c r="C446" t="n">
-        <v>0</v>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="447">
@@ -5355,8 +6244,10 @@
       <c r="B447" t="n">
         <v>503.5</v>
       </c>
-      <c r="C447" t="n">
-        <v>0</v>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="448">
@@ -5366,8 +6257,10 @@
       <c r="B448" t="n">
         <v>508</v>
       </c>
-      <c r="C448" t="n">
-        <v>0</v>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="449">
@@ -5377,8 +6270,10 @@
       <c r="B449" t="n">
         <v>507.1</v>
       </c>
-      <c r="C449" t="n">
-        <v>0</v>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="450">
@@ -5388,8 +6283,10 @@
       <c r="B450" t="n">
         <v>507</v>
       </c>
-      <c r="C450" t="n">
-        <v>0</v>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="451">
@@ -5399,8 +6296,10 @@
       <c r="B451" t="n">
         <v>506</v>
       </c>
-      <c r="C451" t="n">
-        <v>0</v>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="452">
@@ -5410,8 +6309,10 @@
       <c r="B452" t="n">
         <v>509.5</v>
       </c>
-      <c r="C452" t="n">
-        <v>0</v>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="453">
@@ -5421,8 +6322,10 @@
       <c r="B453" t="n">
         <v>513</v>
       </c>
-      <c r="C453" t="n">
-        <v>0</v>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="454">
@@ -5432,8 +6335,10 @@
       <c r="B454" t="n">
         <v>510.5</v>
       </c>
-      <c r="C454" t="n">
-        <v>0</v>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="455">
@@ -5443,8 +6348,10 @@
       <c r="B455" t="n">
         <v>511</v>
       </c>
-      <c r="C455" t="n">
-        <v>0</v>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="456">
@@ -5454,8 +6361,10 @@
       <c r="B456" t="n">
         <v>514.9</v>
       </c>
-      <c r="C456" t="n">
-        <v>0</v>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="457">
@@ -5465,8 +6374,10 @@
       <c r="B457" t="n">
         <v>513.2</v>
       </c>
-      <c r="C457" t="n">
-        <v>0</v>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="458">
@@ -5476,8 +6387,10 @@
       <c r="B458" t="n">
         <v>512</v>
       </c>
-      <c r="C458" t="n">
-        <v>0</v>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="459">
@@ -5487,8 +6400,10 @@
       <c r="B459" t="n">
         <v>510.2</v>
       </c>
-      <c r="C459" t="n">
-        <v>0</v>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="460">
@@ -5498,8 +6413,10 @@
       <c r="B460" t="n">
         <v>503</v>
       </c>
-      <c r="C460" t="n">
-        <v>0</v>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="461">
@@ -5509,8 +6426,10 @@
       <c r="B461" t="n">
         <v>495</v>
       </c>
-      <c r="C461" t="n">
-        <v>0</v>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="462">
@@ -5520,8 +6439,10 @@
       <c r="B462" t="n">
         <v>496</v>
       </c>
-      <c r="C462" t="n">
-        <v>0</v>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="463">
@@ -5531,8 +6452,10 @@
       <c r="B463" t="n">
         <v>494.7</v>
       </c>
-      <c r="C463" t="n">
-        <v>0</v>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
     <row r="464">
@@ -5542,8 +6465,10 @@
       <c r="B464" t="n">
         <v>495</v>
       </c>
-      <c r="C464" t="n">
-        <v>0</v>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -5557,39 +6482,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Pred SELL</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Pred BUY</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>SELL</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4989200863930885</v>
+        <v>246</v>
+      </c>
+      <c r="C2" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Balanced Accuracy</t>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>BUY</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4888981075421753</v>
+        <v>138</v>
+      </c>
+      <c r="C3" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -5603,45 +6534,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Pred SELL</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Pred BUY</t>
+          <t>Importance</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>SELL</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>VWAP_ratio_mean</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
-      </c>
-      <c r="C2" t="n">
-        <v>134</v>
+        <v>0.04559650230973046</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>BUY</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>VWAP_ratio_last</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>98</v>
-      </c>
-      <c r="C3" t="n">
-        <v>79</v>
+        <v>0.04433064389250228</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>OBV_pct_std</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.04235693825251168</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>VWAP_ratio_std</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0332228431045244</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Beta_slope</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.03038220879525282</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Beta_momentum</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.02902476575711066</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Beta_mean</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.02835054736755993</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Beta_last</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.02777130098197282</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ATR_norm_last</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.02651171266409769</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>OBV_pct_last</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.02457930225571562</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RSI_mean</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.02425159424992985</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BB_position_slope</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.02401253435640713</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Beta_std</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.02393623394548986</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>OBV_pct_momentum</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.02388292025998389</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MACD_signal_norm_last</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.02380476103367662</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>OBV_pct_mean</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.02278996242588127</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ATR_norm_mean</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0226443893460097</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>MACD_norm_mean</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.02254505256287247</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EMA_20_ratio_mean</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.02194537703246671</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BB_position_mean</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.02167801405959326</v>
       </c>
     </row>
   </sheetData>
@@ -5655,275 +6760,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Feature</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Importance</t>
+          <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>VWAP_ratio_mean</t>
+          <t>Accuracy</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04559650230973046</v>
+        <v>0.6155507559395248</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>VWAP_ratio_last</t>
+          <t>Balanced Accuracy</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04433064389250228</v>
+        <v>0.5402394215953538</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>OBV_pct_std</t>
+          <t>sharpe_ratio</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04235693825251168</v>
+        <v>0.4019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>VWAP_ratio_std</t>
+          <t>max_drawdown</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0332228431045244</v>
+        <v>-14.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Beta_slope</t>
+          <t>exposure</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03038220879525282</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Beta_momentum</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.02902476575711066</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Beta_mean</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.02835054736755993</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Beta_last</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.02777130098197282</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ATR_norm_last</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.02651171266409769</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OBV_pct_last</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.02457930225571562</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RSI_mean</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>0.02425159424992985</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>BB_position_slope</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>0.02401253435640713</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Beta_std</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>0.02393623394548986</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>OBV_pct_momentum</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0.02388292025998389</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MACD_signal_norm_last</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.02380476103367662</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>OBV_pct_mean</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.02278996242588127</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>ATR_norm_mean</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.0226443893460097</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MACD_norm_mean</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.02254505256287247</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>EMA_20_ratio_mean</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.02194537703246671</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>BB_position_mean</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.02167801405959326</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>sharpe_ratio</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>-0.1471</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>max_drawdown</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-21.77</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>exposure</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>46</v>
+        <v>17.06</v>
       </c>
     </row>
   </sheetData>

--- a/CATI/saved_states/NABIL_backtest_results.xlsx
+++ b/CATI/saved_states/NABIL_backtest_results.xlsx
@@ -526,7 +526,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1449,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2203,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
     </row>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
     </row>
@@ -6504,10 +6504,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
@@ -6517,10 +6517,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -6782,7 +6782,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6155507559395248</v>
+        <v>0.6241900647948164</v>
       </c>
     </row>
     <row r="3">
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5402394215953538</v>
+        <v>0.54507921457074</v>
       </c>
     </row>
     <row r="4">
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4019</v>
+        <v>0.231</v>
       </c>
     </row>
     <row r="5">
@@ -6812,7 +6812,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-14.01</v>
+        <v>-16.57</v>
       </c>
     </row>
     <row r="6">
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.06</v>
+        <v>15.33</v>
       </c>
     </row>
   </sheetData>
